--- a/metricas_realizadas/Prog-Concurrente/2026-PROGC-Q2-M4/TP Metrica/Informes/Plantilla-metrica_M4.xlsx
+++ b/metricas_realizadas/Prog-Concurrente/2026-PROGC-Q2-M4/TP Metrica/Informes/Plantilla-metrica_M4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vicut\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyecto_code_ia\metricas_realizadas\Prog-Concurrente\2026-PROGC-Q2-M4\TP Metrica\Informes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62932893-12F2-4EF0-8093-1D4F6B7C50AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D000AD-E65F-4E25-B3BE-E20165E4355D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1020" yWindow="6120" windowWidth="19200" windowHeight="5100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos del proyecto" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,21 @@
     <sheet name="Concurrencia" sheetId="4" r:id="rId4"/>
     <sheet name="Datos Tokens" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -587,12 +601,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="49" bestFit="1" customWidth="1"/>
   </cols>
@@ -648,15 +662,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
-    <col min="4" max="4" width="38.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="29.1" customHeight="1">
+    <row r="1" spans="1:4" ht="29.15" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -740,22 +754,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" customWidth="1"/>
+    <col min="2" max="2" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" customWidth="1"/>
     <col min="7" max="7" width="40" customWidth="1"/>
-    <col min="8" max="8" width="22.85546875" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="22.81640625" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.95" customHeight="1">
+    <row r="1" spans="1:11" ht="28" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -790,7 +804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30">
+    <row r="2" spans="1:11" ht="29">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -938,16 +952,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
-    <col min="4" max="4" width="38.28515625" customWidth="1"/>
-    <col min="5" max="5" width="30.140625" customWidth="1"/>
+    <col min="1" max="1" width="16.453125" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" customWidth="1"/>
+    <col min="4" max="4" width="38.26953125" customWidth="1"/>
+    <col min="5" max="5" width="30.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1046,12 +1060,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.81640625" customWidth="1"/>
     <col min="2" max="2" width="62" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.54296875" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1082,7 +1096,7 @@
         <v>6700</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30">
+    <row r="3" spans="1:4" ht="29">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1125,8 +1139,14 @@
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="C6" s="1">
+        <f>SUM(C2:C5)</f>
+        <v>12</v>
+      </c>
+      <c r="D6" s="31">
+        <f>SUM(D2:D5)</f>
+        <v>16466877</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="C7" s="1"/>
